--- a/High_Level_Test_Scenario.xlsx
+++ b/High_Level_Test_Scenario.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progress\OrangHRM\All_Documnets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE5712A-D0EA-43EB-96B8-B9C97CA53D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E1128E-F135-4038-BE9B-34CB2829FADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="PIM" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -103,13 +104,103 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
+    <t>Test Scenario ID</t>
+  </si>
+  <si>
+    <t>Verify the PIM menu is displayed after successful login.</t>
+  </si>
+  <si>
+    <t>Verify the user can navigate to the PIM module by clicking the PIM menu.</t>
+  </si>
+  <si>
+    <t>Verify the Employee List page is displayed after navigating to the PIM module.</t>
+  </si>
+  <si>
+    <t>Verify the Employee table is displayed with employee records.</t>
+  </si>
+  <si>
+    <t>Verify the total number of employee records is displayed.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Verify the displayed employee row count matches the Records Found count on the current page.</t>
+  </si>
+  <si>
+    <t>TS-007</t>
+  </si>
+  <si>
+    <t>Verify pagination controls are displayed when multiple employee pages are available.</t>
+  </si>
+  <si>
+    <t>TS-008</t>
+  </si>
+  <si>
+    <t>Verify clicking the Next button navigates to the next page of employee records.</t>
+  </si>
+  <si>
+    <t>TS-009</t>
+  </si>
+  <si>
+    <t>Verify a new employee can be added successfully and the Personal Details page is displayed.</t>
+  </si>
+  <si>
+    <t>TS-010</t>
+  </si>
+  <si>
+    <t>TS-011</t>
+  </si>
+  <si>
+    <t>TS-012</t>
+  </si>
+  <si>
+    <t>TS-013</t>
+  </si>
+  <si>
+    <t>TS-014</t>
+  </si>
+  <si>
+    <t>TS-015</t>
+  </si>
+  <si>
+    <t>FR-07</t>
+  </si>
+  <si>
+    <t>FR-08</t>
+  </si>
+  <si>
+    <t>FR-09</t>
+  </si>
+  <si>
+    <t>FR-10</t>
+  </si>
+  <si>
+    <t>FR-11</t>
+  </si>
+  <si>
+    <t>FR-12</t>
+  </si>
+  <si>
+    <t>FR-13</t>
+  </si>
+  <si>
+    <t>FR-14</t>
+  </si>
+  <si>
+    <t>FR-15, FR-16</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +211,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0F4761"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -145,15 +250,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,133 +548,319 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="61.5546875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="61.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B896596-BBCE-437C-A965-3BE6B60C10C7}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="5"/>
+    <col min="4" max="4" width="31.109375" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/High_Level_Test_Scenario.xlsx
+++ b/High_Level_Test_Scenario.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progress\OrangHRM\All_Documnets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E1128E-F135-4038-BE9B-34CB2829FADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CFD8F2-458B-4AD3-B901-9B82939571EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="PIM" sheetId="3" r:id="rId2"/>
+    <sheet name="Admin" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,14 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
   <si>
     <t>Scenario ID</t>
   </si>
   <si>
-    <t>Requirement ID</t>
-  </si>
-  <si>
     <t>Module</t>
   </si>
   <si>
@@ -43,9 +41,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>FR-01</t>
-  </si>
-  <si>
     <t>TS-001</t>
   </si>
   <si>
@@ -61,27 +56,18 @@
     <t>TS-002</t>
   </si>
   <si>
-    <t>FR-02</t>
-  </si>
-  <si>
     <t>Verify credential validation functionality before granting access</t>
   </si>
   <si>
     <t>TS-003</t>
   </si>
   <si>
-    <t>FR-03</t>
-  </si>
-  <si>
     <t>Verify error handling for invalid login attempts</t>
   </si>
   <si>
     <t>TS-004</t>
   </si>
   <si>
-    <t>FR-04</t>
-  </si>
-  <si>
     <t>Verify account lock functionality after consecutive failed login attempts</t>
   </si>
   <si>
@@ -91,18 +77,12 @@
     <t>TS-006</t>
   </si>
   <si>
-    <t>FR-05</t>
-  </si>
-  <si>
     <t>Verify Forgot Password functionality for registered users</t>
   </si>
   <si>
     <t>Verify social media icons redirect users to the correct social media pages.</t>
   </si>
   <si>
-    <t>FR-06</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -169,48 +149,62 @@
     <t>TS-015</t>
   </si>
   <si>
-    <t>FR-07</t>
-  </si>
-  <si>
-    <t>FR-08</t>
-  </si>
-  <si>
-    <t>FR-09</t>
-  </si>
-  <si>
-    <t>FR-10</t>
-  </si>
-  <si>
-    <t>FR-11</t>
-  </si>
-  <si>
-    <t>FR-12</t>
-  </si>
-  <si>
-    <t>FR-13</t>
-  </si>
-  <si>
-    <t>FR-14</t>
-  </si>
-  <si>
-    <t>FR-15, FR-16</t>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Verify that the Admin User List page is displayed successfully.</t>
+  </si>
+  <si>
+    <t>Verify that all available users are displayed in the user list table.</t>
+  </si>
+  <si>
+    <t>Verify that the User List table displays the Username column.</t>
+  </si>
+  <si>
+    <t>TS-016</t>
+  </si>
+  <si>
+    <t>Verify that the User List table displays the User Role column.</t>
+  </si>
+  <si>
+    <t>TS-017</t>
+  </si>
+  <si>
+    <t>Verify that the User List table displays the Employee Name column.</t>
+  </si>
+  <si>
+    <t>TS-018</t>
+  </si>
+  <si>
+    <t>Verify that the User List table displays the Status column.</t>
+  </si>
+  <si>
+    <t>TS-019</t>
+  </si>
+  <si>
+    <t>Verify that the User List table displays the Actions column.</t>
+  </si>
+  <si>
+    <t>TS-020</t>
+  </si>
+  <si>
+    <t>Verify that pagination is displayed when the number of user records exceeds one page.</t>
+  </si>
+  <si>
+    <t>TS-021</t>
+  </si>
+  <si>
+    <t>Verify that the user can navigate between pages using pagination controls.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0F4761"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -250,18 +244,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -545,15 +536,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="61.5546875" customWidth="1"/>
+    <col min="3" max="3" width="61.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,110 +556,89 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -679,188 +648,311 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B896596-BBCE-437C-A965-3BE6B60C10C7}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="5"/>
-    <col min="4" max="4" width="31.109375" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60025B5-91FC-4158-A37D-BB34CFC8CD6B}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="38.88671875" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="10" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/High_Level_Test_Scenario.xlsx
+++ b/High_Level_Test_Scenario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progress\OrangHRM\All_Documnets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CFD8F2-458B-4AD3-B901-9B82939571EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74480AC-CB68-4264-B0A6-D8A192ECF4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="74">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -152,49 +152,103 @@
     <t>Admin</t>
   </si>
   <si>
-    <t>Verify that the Admin User List page is displayed successfully.</t>
-  </si>
-  <si>
-    <t>Verify that all available users are displayed in the user list table.</t>
-  </si>
-  <si>
-    <t>Verify that the User List table displays the Username column.</t>
-  </si>
-  <si>
     <t>TS-016</t>
   </si>
   <si>
-    <t>Verify that the User List table displays the User Role column.</t>
-  </si>
-  <si>
     <t>TS-017</t>
   </si>
   <si>
-    <t>Verify that the User List table displays the Employee Name column.</t>
-  </si>
-  <si>
     <t>TS-018</t>
   </si>
   <si>
-    <t>Verify that the User List table displays the Status column.</t>
-  </si>
-  <si>
     <t>TS-019</t>
   </si>
   <si>
-    <t>Verify that the User List table displays the Actions column.</t>
-  </si>
-  <si>
     <t>TS-020</t>
   </si>
   <si>
-    <t>Verify that pagination is displayed when the number of user records exceeds one page.</t>
-  </si>
-  <si>
     <t>TS-021</t>
   </si>
   <si>
-    <t>Verify that the user can navigate between pages using pagination controls.</t>
+    <t>Verify Admin menu is displayed after successful login.</t>
+  </si>
+  <si>
+    <t>Verify user is able to open the Admin module.</t>
+  </si>
+  <si>
+    <t>Verify Add User page is displayed when clicking the Add button.</t>
+  </si>
+  <si>
+    <t>Verify a new user can be added with valid details.</t>
+  </si>
+  <si>
+    <t>Verify mandatory fields are validated while adding a user.</t>
+  </si>
+  <si>
+    <t>Verify unique username validation while creating a user.</t>
+  </si>
+  <si>
+    <t>Verify user can search by Username.</t>
+  </si>
+  <si>
+    <t>Verify user can search by User Role.</t>
+  </si>
+  <si>
+    <t>Verify user can search by Employee Name.</t>
+  </si>
+  <si>
+    <t>TS-022</t>
+  </si>
+  <si>
+    <t>Verify user can search by Status (Enabled/Disabled).</t>
+  </si>
+  <si>
+    <t>TS-023</t>
+  </si>
+  <si>
+    <t>Verify search results display matching user records.</t>
+  </si>
+  <si>
+    <t>TS-024</t>
+  </si>
+  <si>
+    <t>Verify Reset button clears all search fields.</t>
+  </si>
+  <si>
+    <t>TS-025</t>
+  </si>
+  <si>
+    <t>Verify existing user details can be edited successfully.</t>
+  </si>
+  <si>
+    <t>TS-026</t>
+  </si>
+  <si>
+    <t>Verify existing user can be deleted successfully.</t>
+  </si>
+  <si>
+    <t>TS-027</t>
+  </si>
+  <si>
+    <t>Verify deleted user is removed from the user list.</t>
+  </si>
+  <si>
+    <t>TS-028</t>
+  </si>
+  <si>
+    <t>Verify user list is displayed with all available users.</t>
+  </si>
+  <si>
+    <t>TS-029</t>
+  </si>
+  <si>
+    <t>Verify pagination works correctly when multiple users are available.</t>
+  </si>
+  <si>
+    <t>TS-030</t>
+  </si>
+  <si>
+    <t>Verify column sorting works correctly (if available).</t>
   </si>
 </sst>
 </file>
@@ -244,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -255,7 +309,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,16 +856,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60025B5-91FC-4158-A37D-BB34CFC8CD6B}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="57.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -826,7 +878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
@@ -834,13 +886,13 @@
         <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
@@ -848,13 +900,13 @@
         <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>39</v>
       </c>
@@ -862,85 +914,85 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>40</v>
@@ -950,6 +1002,132 @@
       </c>
       <c r="D10" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
